--- a/users.xlsx
+++ b/users.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>firstName</t>
   </si>
@@ -30,13 +30,31 @@
     <t>email</t>
   </si>
   <si>
-    <t>Joe</t>
-  </si>
-  <si>
-    <t>EPOU</t>
-  </si>
-  <si>
-    <t>joe@gmail.com</t>
+    <t>Mathieu</t>
+  </si>
+  <si>
+    <t>Sylvie</t>
+  </si>
+  <si>
+    <t>Mael</t>
+  </si>
+  <si>
+    <t>Elior</t>
+  </si>
+  <si>
+    <t>AWOKOU</t>
+  </si>
+  <si>
+    <t>sylvie@gmail.com</t>
+  </si>
+  <si>
+    <t>mael@gmail.com</t>
+  </si>
+  <si>
+    <t>elior@gmail.com</t>
+  </si>
+  <si>
+    <t>mathieu@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -365,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -389,20 +407,53 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C3" s="1"/>
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId5"/>
 </worksheet>
 </file>